--- a/quickbook_summary.xlsx
+++ b/quickbook_summary.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3098,10 +3098,8 @@
       <c r="G73" s="4" t="n">
         <v>11407.5</v>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="74">
@@ -3136,10 +3134,8 @@
       <c r="G74" s="4" t="n">
         <v>54602.32</v>
       </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="75">
@@ -3174,10 +3170,8 @@
       <c r="G75" s="4" t="n">
         <v>50518</v>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="76">
@@ -3212,10 +3206,8 @@
       <c r="G76" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H76" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="77">
@@ -3250,10 +3242,8 @@
       <c r="G77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H77" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="78">
@@ -3288,10 +3278,224 @@
       <c r="G78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>4003 · Mobilization Income</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>NGSJ25-013</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>402 Concrete Insulating and Vapor Plenum</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>4003 · Mobilization Income</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>NGSJ25-013</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>501 Installation and Construction Labor</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>54602.32</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>4003 · Mobilization Income</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>NGSJ25-013</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>502 Wellfield Conveyance,Natural gas regulators and fittings</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>50518</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>4003 · Mobilization Income</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>NGSJ25-013</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>503 Treatment System Electrical</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>9133.33</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>4003 · Mobilization Income</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>NGSJ25-013</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>504 PLC, SCADA Programming, Telemetrics</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>1638</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>4003 · Mobilization Income</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>NGSJ25-013</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>505 Commissioning and Shakedown</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -3305,7 +3509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -15178,35 +15382,31 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D335" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> $3267280.002</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr"/>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1 X 2 STD BLACK NIPPLE TBE</t>
+          <t>Michael H &amp; Vace V	Hotel- 12/8-12/21</t>
         </is>
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G335" s="4" t="n">
-        <v>13.48</v>
+        <v>1016.4</v>
       </c>
       <c r="H335" s="5" t="n">
         <v>500</v>
@@ -15214,35 +15414,31 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
-        <v>46013</v>
+        <v>46011</v>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D336" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> $3267280.002</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr"/>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2 X 1 STD BLACK BELL REDUCER</t>
+          <t>EMILY G SANDOVAL-81047-173608      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G336" s="4" t="n">
-        <v>71.62</v>
+        <v>101.64</v>
       </c>
       <c r="H336" s="5" t="n">
         <v>500</v>
@@ -15269,7 +15465,7 @@
       </c>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t xml:space="preserve"> 1 X 2 STD BLACK NIPPLE TBE</t>
         </is>
       </c>
       <c r="F337" s="3" t="inlineStr">
@@ -15278,7 +15474,7 @@
         </is>
       </c>
       <c r="G337" s="4" t="n">
-        <v>6.6</v>
+        <v>13.48</v>
       </c>
       <c r="H337" s="5" t="n">
         <v>500</v>
@@ -15286,11 +15482,11 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C338" s="3" t="inlineStr">
@@ -15300,12 +15496,12 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>177786256-0002</t>
+          <t xml:space="preserve"> $3267280.002</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>0 10K 42'-48' TELEHANDLER FORKLIFT</t>
+          <t xml:space="preserve"> 2 X 1 STD BLACK BELL REDUCER</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr">
@@ -15314,7 +15510,7 @@
         </is>
       </c>
       <c r="G338" s="4" t="n">
-        <v>3935</v>
+        <v>71.62</v>
       </c>
       <c r="H338" s="5" t="n">
         <v>500</v>
@@ -15322,11 +15518,11 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C339" s="3" t="inlineStr">
@@ -15336,12 +15532,12 @@
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>177786256-0002</t>
+          <t xml:space="preserve"> $3267280.002</t>
         </is>
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F339" s="3" t="inlineStr">
@@ -15350,7 +15546,7 @@
         </is>
       </c>
       <c r="G339" s="4" t="n">
-        <v>202.49</v>
+        <v>6.6</v>
       </c>
       <c r="H339" s="5" t="n">
         <v>500</v>
@@ -15377,7 +15573,7 @@
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>0 10K 42'-48' TELEHANDLER FORKLIFT</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr">
@@ -15386,7 +15582,7 @@
         </is>
       </c>
       <c r="G340" s="4" t="n">
-        <v>387.89</v>
+        <v>3935</v>
       </c>
       <c r="H340" s="5" t="n">
         <v>500</v>
@@ -15394,7 +15590,7 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
-        <v>46016</v>
+        <v>46014</v>
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
@@ -15408,12 +15604,12 @@
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>252549305-005</t>
+          <t>177786256-0002</t>
         </is>
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>375/0525 FENCE MODULAR 12' L X 6' H TEMPORARY PAN</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="F341" s="3" t="inlineStr">
@@ -15422,7 +15618,7 @@
         </is>
       </c>
       <c r="G341" s="4" t="n">
-        <v>58.1</v>
+        <v>202.49</v>
       </c>
       <c r="H341" s="5" t="n">
         <v>500</v>
@@ -15430,7 +15626,7 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
-        <v>46016</v>
+        <v>46014</v>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
@@ -15444,12 +15640,12 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>252549305-005</t>
+          <t>177786256-0002</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Fence Wheel and weight</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr">
@@ -15458,7 +15654,7 @@
         </is>
       </c>
       <c r="G342" s="4" t="n">
-        <v>65</v>
+        <v>387.89</v>
       </c>
       <c r="H342" s="5" t="n">
         <v>500</v>
@@ -15485,7 +15681,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>Service Charge and Tax</t>
+          <t>375/0525 FENCE MODULAR 12' L X 6' H TEMPORARY PAN</t>
         </is>
       </c>
       <c r="F343" s="3" t="inlineStr">
@@ -15494,7 +15690,7 @@
         </is>
       </c>
       <c r="G343" s="4" t="n">
-        <v>12.2</v>
+        <v>58.1</v>
       </c>
       <c r="H343" s="5" t="n">
         <v>500</v>
@@ -15502,11 +15698,11 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>46020</v>
+        <v>46016</v>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C344" s="3" t="inlineStr">
@@ -15516,12 +15712,12 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>1611044815</t>
+          <t>252549305-005</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>1 X 6 BLACK NIPPLE</t>
+          <t>Fence Wheel and weight</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr">
@@ -15530,7 +15726,7 @@
         </is>
       </c>
       <c r="G344" s="4" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="H344" s="5" t="n">
         <v>500</v>
@@ -15538,11 +15734,11 @@
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>46020</v>
+        <v>46016</v>
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C345" s="3" t="inlineStr">
@@ -15552,12 +15748,12 @@
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>1611044815</t>
+          <t>252549305-005</t>
         </is>
       </c>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>2 150# RF SLIP-ON WELD FLANGE A105 TRANSFER# 121910485196L1 HEAT</t>
+          <t>Service Charge and Tax</t>
         </is>
       </c>
       <c r="F345" s="3" t="inlineStr">
@@ -15566,7 +15762,7 @@
         </is>
       </c>
       <c r="G345" s="4" t="n">
-        <v>492.5</v>
+        <v>12.2</v>
       </c>
       <c r="H345" s="5" t="n">
         <v>500</v>
@@ -15593,7 +15789,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>2 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+          <t>1 X 6 BLACK NIPPLE</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr">
@@ -15602,7 +15798,7 @@
         </is>
       </c>
       <c r="G346" s="4" t="n">
-        <v>31.5</v>
+        <v>114</v>
       </c>
       <c r="H346" s="5" t="n">
         <v>500</v>
@@ -15629,7 +15825,7 @@
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
+          <t>2 150# RF SLIP-ON WELD FLANGE A105 TRANSFER# 121910485196L1 HEAT</t>
         </is>
       </c>
       <c r="F347" s="3" t="inlineStr">
@@ -15638,7 +15834,7 @@
         </is>
       </c>
       <c r="G347" s="4" t="n">
-        <v>363</v>
+        <v>492.5</v>
       </c>
       <c r="H347" s="5" t="n">
         <v>500</v>
@@ -15665,7 +15861,7 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>2 CAP WELD HEAT</t>
+          <t>2 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr">
@@ -15674,7 +15870,7 @@
         </is>
       </c>
       <c r="G348" s="4" t="n">
-        <v>28.8</v>
+        <v>31.5</v>
       </c>
       <c r="H348" s="5" t="n">
         <v>500</v>
@@ -15701,7 +15897,7 @@
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>TAx</t>
+          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
         </is>
       </c>
       <c r="F349" s="3" t="inlineStr">
@@ -15710,7 +15906,7 @@
         </is>
       </c>
       <c r="G349" s="4" t="n">
-        <v>96.54000000000001</v>
+        <v>363</v>
       </c>
       <c r="H349" s="5" t="n">
         <v>500</v>
@@ -15718,11 +15914,11 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>5120 · Outside services (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C350" s="3" t="inlineStr">
@@ -15732,12 +15928,12 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>3185084481</t>
+          <t>1611044815</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Service Labor</t>
+          <t>2 CAP WELD HEAT</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr">
@@ -15746,7 +15942,7 @@
         </is>
       </c>
       <c r="G350" s="4" t="n">
-        <v>500</v>
+        <v>28.8</v>
       </c>
       <c r="H350" s="5" t="n">
         <v>500</v>
@@ -15754,35 +15950,35 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>46028</v>
+        <v>46020</v>
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>1611044815</t>
         </is>
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt Per diem for week of 12/29/2026 - 1/11/2026</t>
+          <t>TAx</t>
         </is>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G351" s="4" t="n">
-        <v>700</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="H351" s="5" t="n">
         <v>500</v>
@@ -15790,7 +15986,7 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>46028</v>
+        <v>46021</v>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
@@ -15804,12 +16000,12 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>719750SJ</t>
+          <t>3185084481</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Power Plus will install 3ph 200amp meter on a 30ft diamond pole use 1 span of gruillo to connect...</t>
+          <t>Service Labor</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr">
@@ -15818,7 +16014,7 @@
         </is>
       </c>
       <c r="G352" s="4" t="n">
-        <v>11625</v>
+        <v>500</v>
       </c>
       <c r="H352" s="5" t="n">
         <v>500</v>
@@ -15826,11 +16022,11 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>6125 · Utilities (Indirect)</t>
         </is>
       </c>
       <c r="C353" s="3" t="inlineStr">
@@ -15840,21 +16036,17 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>1611068138</t>
-        </is>
-      </c>
-      <c r="E353" s="3" t="inlineStr">
-        <is>
-          <t>2 BLK PE A53B SCH40 STEEL PIPE .154W HEAT</t>
-        </is>
-      </c>
+          <t>5009904638</t>
+        </is>
+      </c>
+      <c r="E353" s="3" t="inlineStr"/>
       <c r="F353" s="3" t="inlineStr">
         <is>
           <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G353" s="4" t="n">
-        <v>1368.71</v>
+        <v>118.18</v>
       </c>
       <c r="H353" s="5" t="n">
         <v>500</v>
@@ -15862,35 +16054,31 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5105 · Travel - Airfare (Direct)</t>
         </is>
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D354" s="3" t="inlineStr">
-        <is>
-          <t>1611068138</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr"/>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>1 X 6 BLACK NIPPLE</t>
+          <t>Vace Varasteh	Flight- SJC to SNA 1/8</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G354" s="4" t="n">
-        <v>114.9</v>
+        <v>375.48</v>
       </c>
       <c r="H354" s="5" t="n">
         <v>500</v>
@@ -15898,35 +16086,35 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>1611068138</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>2 X 6 BLACK NIPPLE</t>
+          <t>Michael Hyatt Per diem for week of 12/29/2026 - 1/11/2026</t>
         </is>
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="G355" s="4" t="n">
-        <v>191.64</v>
+        <v>700</v>
       </c>
       <c r="H355" s="5" t="n">
         <v>500</v>
@@ -15934,11 +16122,11 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5120 · Outside services (Direct)</t>
         </is>
       </c>
       <c r="C356" s="3" t="inlineStr">
@@ -15948,12 +16136,12 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>1611068138</t>
+          <t>719750SJ</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>2 LONG RADIUS 45 ELBOW WELD HEAT #______________________________</t>
+          <t>Power Plus will install 3ph 200amp meter on a 30ft diamond pole use 1 span of gruillo to connect...</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr">
@@ -15962,7 +16150,7 @@
         </is>
       </c>
       <c r="G356" s="4" t="n">
-        <v>84.95999999999999</v>
+        <v>11625</v>
       </c>
       <c r="H356" s="5" t="n">
         <v>500</v>
@@ -15989,7 +16177,7 @@
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>2 CAP WELD HEAT</t>
+          <t>2 BLK PE A53B SCH40 STEEL PIPE .154W HEAT</t>
         </is>
       </c>
       <c r="F357" s="3" t="inlineStr">
@@ -15998,7 +16186,7 @@
         </is>
       </c>
       <c r="G357" s="4" t="n">
-        <v>57.6</v>
+        <v>1368.71</v>
       </c>
       <c r="H357" s="5" t="n">
         <v>500</v>
@@ -16025,7 +16213,7 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>3 X 2 CONC REDUCER WELD HEAT</t>
+          <t>1 X 6 BLACK NIPPLE</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr">
@@ -16034,7 +16222,7 @@
         </is>
       </c>
       <c r="G358" s="4" t="n">
-        <v>69</v>
+        <v>114.9</v>
       </c>
       <c r="H358" s="5" t="n">
         <v>500</v>
@@ -16061,7 +16249,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>3 TEE WELD HEAT</t>
+          <t>2 X 6 BLACK NIPPLE</t>
         </is>
       </c>
       <c r="F359" s="3" t="inlineStr">
@@ -16070,7 +16258,7 @@
         </is>
       </c>
       <c r="G359" s="4" t="n">
-        <v>72.84</v>
+        <v>191.64</v>
       </c>
       <c r="H359" s="5" t="n">
         <v>500</v>
@@ -16097,7 +16285,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>2 LONG RADIUS 90 ELBOW WELD HEAT</t>
+          <t>2 LONG RADIUS 45 ELBOW WELD HEAT #______________________________</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr">
@@ -16106,7 +16294,7 @@
         </is>
       </c>
       <c r="G360" s="4" t="n">
-        <v>17.71</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="H360" s="5" t="n">
         <v>500</v>
@@ -16133,7 +16321,7 @@
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>2 CAP WELD HEAT</t>
         </is>
       </c>
       <c r="F361" s="3" t="inlineStr">
@@ -16142,7 +16330,7 @@
         </is>
       </c>
       <c r="G361" s="4" t="n">
-        <v>185.38</v>
+        <v>57.6</v>
       </c>
       <c r="H361" s="5" t="n">
         <v>500</v>
@@ -16150,7 +16338,7 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
@@ -16164,12 +16352,12 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>S3276236.001</t>
+          <t>1611068138</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>150 x 1/16 FF EPDM GASKET</t>
+          <t>3 X 2 CONC REDUCER WELD HEAT</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr">
@@ -16178,7 +16366,7 @@
         </is>
       </c>
       <c r="G362" s="4" t="n">
-        <v>3.06</v>
+        <v>69</v>
       </c>
       <c r="H362" s="5" t="n">
         <v>500</v>
@@ -16186,7 +16374,7 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
@@ -16200,12 +16388,12 @@
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>S3276236.001</t>
+          <t>1611068138</t>
         </is>
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>1 PINT BLUE MONSTER</t>
+          <t>3 TEE WELD HEAT</t>
         </is>
       </c>
       <c r="F363" s="3" t="inlineStr">
@@ -16214,7 +16402,7 @@
         </is>
       </c>
       <c r="G363" s="4" t="n">
-        <v>50.12</v>
+        <v>72.84</v>
       </c>
       <c r="H363" s="5" t="n">
         <v>500</v>
@@ -16222,7 +16410,7 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
@@ -16236,12 +16424,12 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>S3276236.001</t>
+          <t>1611068138</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>1/2 x 260 Yellow Gas Line</t>
+          <t>2 LONG RADIUS 90 ELBOW WELD HEAT</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr">
@@ -16250,7 +16438,7 @@
         </is>
       </c>
       <c r="G364" s="4" t="n">
-        <v>22.72</v>
+        <v>17.71</v>
       </c>
       <c r="H364" s="5" t="n">
         <v>500</v>
@@ -16258,7 +16446,7 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
@@ -16272,12 +16460,12 @@
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>S3276236.001</t>
+          <t>1611068138</t>
         </is>
       </c>
       <c r="E365" s="3" t="inlineStr">
         <is>
-          <t>3/4 x 1429 BLUE MONSTER</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F365" s="3" t="inlineStr">
@@ -16286,7 +16474,7 @@
         </is>
       </c>
       <c r="G365" s="4" t="n">
-        <v>5.7</v>
+        <v>185.38</v>
       </c>
       <c r="H365" s="5" t="n">
         <v>500</v>
@@ -16294,35 +16482,31 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D366" s="3" t="inlineStr">
-        <is>
-          <t>S3276236.001</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr"/>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Michael Hyatt	Hotel- 12/29-1/12</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G366" s="4" t="n">
-        <v>6.33</v>
+        <v>1016.4</v>
       </c>
       <c r="H366" s="5" t="n">
         <v>500</v>
@@ -16330,111 +16514,95 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D367" s="3" t="inlineStr">
-        <is>
-          <t>9771267425</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr"/>
       <c r="E367" s="3" t="inlineStr">
         <is>
-          <t>THREE BEAM MAGNETIC TORPEDO LASER LEVEL</t>
+          <t>Vace Varasteh	Hotel- 12/29-1/12</t>
         </is>
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G367" s="4" t="n">
-        <v>189.76</v>
-      </c>
-      <c r="H367" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>1016.4</v>
+      </c>
+      <c r="H367" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D368" s="3" t="inlineStr">
-        <is>
-          <t>9771267425</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr"/>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>EMILY G SANDOVAL-81047-181717      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G368" s="4" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="H368" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>406.56</v>
+      </c>
+      <c r="H368" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
-        </is>
-      </c>
-      <c r="D369" s="3" t="inlineStr">
-        <is>
-          <t>16810</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="inlineStr"/>
       <c r="E369" s="3" t="inlineStr">
         <is>
-          <t>Luke Giguere Per diem for week of 1/19/2026 - 1/25/2026</t>
+          <t>EMILY G SANDOVAL-81047-181718      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
         </is>
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G369" s="4" t="n">
-        <v>350</v>
+        <v>406.56</v>
       </c>
       <c r="H369" s="5" t="n">
         <v>500</v>
@@ -16442,35 +16610,31 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5107 · Travel - Other (Direct)</t>
         </is>
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
-        </is>
-      </c>
-      <c r="D370" s="3" t="inlineStr">
-        <is>
-          <t>16810</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr"/>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt Per diem for week of 1/12/2026 - 1/25/2026</t>
+          <t>Luke Gigure	Flight- BGR to SJC 1/19</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G370" s="4" t="n">
-        <v>700</v>
+        <v>725.6</v>
       </c>
       <c r="H370" s="5" t="n">
         <v>500</v>
@@ -16478,11 +16642,11 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C371" s="3" t="inlineStr">
@@ -16492,12 +16656,12 @@
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>178433028-0001</t>
+          <t>S3276236.001</t>
         </is>
       </c>
       <c r="E371" s="3" t="inlineStr">
         <is>
-          <t>10K 42'-48' TELEHANDLER FORKLIFT</t>
+          <t>150 x 1/16 FF EPDM GASKET</t>
         </is>
       </c>
       <c r="F371" s="3" t="inlineStr">
@@ -16506,7 +16670,7 @@
         </is>
       </c>
       <c r="G371" s="4" t="n">
-        <v>4470</v>
+        <v>3.06</v>
       </c>
       <c r="H371" s="5" t="n">
         <v>500</v>
@@ -16514,11 +16678,11 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C372" s="3" t="inlineStr">
@@ -16528,12 +16692,12 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>178433028-0001</t>
+          <t>S3276236.001</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Fees and Charges</t>
+          <t>1 PINT BLUE MONSTER</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr">
@@ -16542,7 +16706,7 @@
         </is>
       </c>
       <c r="G372" s="4" t="n">
-        <v>190.69</v>
+        <v>50.12</v>
       </c>
       <c r="H372" s="5" t="n">
         <v>500</v>
@@ -16550,11 +16714,11 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C373" s="3" t="inlineStr">
@@ -16564,12 +16728,12 @@
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>178433028-0001</t>
+          <t>S3276236.001</t>
         </is>
       </c>
       <c r="E373" s="3" t="inlineStr">
         <is>
-          <t>Delivery &amp; Pick Up Charge</t>
+          <t>1/2 x 260 Yellow Gas Line</t>
         </is>
       </c>
       <c r="F373" s="3" t="inlineStr">
@@ -16578,7 +16742,7 @@
         </is>
       </c>
       <c r="G373" s="4" t="n">
-        <v>400</v>
+        <v>22.72</v>
       </c>
       <c r="H373" s="5" t="n">
         <v>500</v>
@@ -16586,11 +16750,11 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C374" s="3" t="inlineStr">
@@ -16600,12 +16764,12 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>178433028-0001</t>
+          <t>S3276236.001</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>3/4 x 1429 BLUE MONSTER</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr">
@@ -16614,7 +16778,7 @@
         </is>
       </c>
       <c r="G374" s="4" t="n">
-        <v>455.68</v>
+        <v>5.7</v>
       </c>
       <c r="H374" s="5" t="n">
         <v>500</v>
@@ -16622,7 +16786,7 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
@@ -16636,12 +16800,12 @@
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>58310926</t>
+          <t>S3276236.001</t>
         </is>
       </c>
       <c r="E375" s="3" t="inlineStr">
         <is>
-          <t>316 Stainless Steel Check Valve with Fluoroelastomer Piston with Rubber</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F375" s="3" t="inlineStr">
@@ -16650,7 +16814,7 @@
         </is>
       </c>
       <c r="G375" s="4" t="n">
-        <v>787.6799999999999</v>
+        <v>6.33</v>
       </c>
       <c r="H375" s="5" t="n">
         <v>500</v>
@@ -16658,7 +16822,7 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
@@ -16672,12 +16836,12 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>58310926</t>
+          <t>9771267425</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>THREE BEAM MAGNETIC TORPEDO LASER LEVEL</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr">
@@ -16686,7 +16850,7 @@
         </is>
       </c>
       <c r="G376" s="4" t="n">
-        <v>43.32</v>
+        <v>189.76</v>
       </c>
       <c r="H376" s="5" t="n">
         <v>500</v>
@@ -16694,7 +16858,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
@@ -16708,12 +16872,12 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>9775828545</t>
+          <t>9771267425</t>
         </is>
       </c>
       <c r="E377" s="3" t="inlineStr">
         <is>
-          <t>V-BELT PULLEY,DETACHABLE,3GROOVE,7.75"O</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F377" s="3" t="inlineStr">
@@ -16722,83 +16886,79 @@
         </is>
       </c>
       <c r="G377" s="4" t="n">
-        <v>222.11</v>
-      </c>
-      <c r="H377" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>14.71</v>
+      </c>
+      <c r="H377" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>9775828545</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Luke Giguere Per diem for week of 1/19/2026 - 1/25/2026</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="G378" s="4" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="H378" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>350</v>
+      </c>
+      <c r="H378" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>58310926</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Michael Hyatt Per diem for week of 1/12/2026 - 1/25/2026</t>
         </is>
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="G379" s="4" t="n">
-        <v>16.44</v>
+        <v>700</v>
       </c>
       <c r="H379" s="5" t="n">
         <v>500</v>
@@ -16806,11 +16966,11 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C380" s="3" t="inlineStr">
@@ -16820,12 +16980,12 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>58542308</t>
+          <t>178433028-0001</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Felt Filter Bag for Water, Sewn Seam, 7" Diameter</t>
+          <t>10K 42'-48' TELEHANDLER FORKLIFT</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr">
@@ -16834,21 +16994,19 @@
         </is>
       </c>
       <c r="G380" s="4" t="n">
-        <v>228.25</v>
-      </c>
-      <c r="H380" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>4470</v>
+      </c>
+      <c r="H380" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C381" s="3" t="inlineStr">
@@ -16858,12 +17016,12 @@
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>58542308</t>
+          <t>178433028-0001</t>
         </is>
       </c>
       <c r="E381" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Fees and Charges</t>
         </is>
       </c>
       <c r="F381" s="3" t="inlineStr">
@@ -16872,21 +17030,19 @@
         </is>
       </c>
       <c r="G381" s="4" t="n">
-        <v>17.69</v>
-      </c>
-      <c r="H381" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>190.69</v>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C382" s="3" t="inlineStr">
@@ -16896,12 +17052,12 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>1611105730</t>
+          <t>178433028-0001</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>2 LONG RADIUS 45 ELBOW WELD HEAT</t>
+          <t>Delivery &amp; Pick Up Charge</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr">
@@ -16910,21 +17066,19 @@
         </is>
       </c>
       <c r="G382" s="4" t="n">
-        <v>84.95999999999999</v>
-      </c>
-      <c r="H382" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>400</v>
+      </c>
+      <c r="H382" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C383" s="3" t="inlineStr">
@@ -16934,12 +17088,12 @@
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>1611105730</t>
+          <t>178433028-0001</t>
         </is>
       </c>
       <c r="E383" s="3" t="inlineStr">
         <is>
-          <t>WLDCAP2</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F383" s="3" t="inlineStr">
@@ -16948,17 +17102,15 @@
         </is>
       </c>
       <c r="G383" s="4" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="H383" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>455.68</v>
+      </c>
+      <c r="H383" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
@@ -16972,12 +17124,12 @@
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>1611105730</t>
+          <t>58310926</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>2 LONG RADIUS 90 ELBOW WELD HEAT</t>
+          <t>316 Stainless Steel Check Valve with Fluoroelastomer Piston with Rubber</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr">
@@ -16986,17 +17138,15 @@
         </is>
       </c>
       <c r="G384" s="4" t="n">
-        <v>265.65</v>
-      </c>
-      <c r="H384" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>787.6799999999999</v>
+      </c>
+      <c r="H384" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
@@ -17010,12 +17160,12 @@
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>1611105730</t>
+          <t>58310926</t>
         </is>
       </c>
       <c r="E385" s="3" t="inlineStr">
         <is>
-          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F385" s="3" t="inlineStr">
@@ -17024,17 +17174,15 @@
         </is>
       </c>
       <c r="G385" s="4" t="n">
-        <v>202.6</v>
-      </c>
-      <c r="H385" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>43.32</v>
+      </c>
+      <c r="H385" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
@@ -17048,12 +17196,12 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>1611105730</t>
+          <t>9775828545</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>2 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+          <t>V-BELT PULLEY,DETACHABLE,3GROOVE,7.75"O</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr">
@@ -17062,17 +17210,15 @@
         </is>
       </c>
       <c r="G386" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="H386" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>222.11</v>
+      </c>
+      <c r="H386" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
@@ -17086,12 +17232,12 @@
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>1611105730</t>
+          <t>9775828545</t>
         </is>
       </c>
       <c r="E387" s="3" t="inlineStr">
         <is>
-          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F387" s="3" t="inlineStr">
@@ -17100,21 +17246,19 @@
         </is>
       </c>
       <c r="G387" s="4" t="n">
-        <v>290.4</v>
-      </c>
-      <c r="H387" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>17.22</v>
+      </c>
+      <c r="H387" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C388" s="3" t="inlineStr">
@@ -17124,12 +17268,12 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>1611105730</t>
+          <t>58310926</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>2 TEE WELD HEAT</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr">
@@ -17138,12 +17282,10 @@
         </is>
       </c>
       <c r="G388" s="4" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="H388" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>16.44</v>
+      </c>
+      <c r="H388" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="389">
@@ -17152,36 +17294,30 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5105 · Travel - Airfare (Direct)</t>
         </is>
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D389" s="3" t="inlineStr">
-        <is>
-          <t>1611105730</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="inlineStr"/>
       <c r="E389" s="3" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>Vace Varasteh	Flight- SNA to SJC 1/26</t>
         </is>
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G389" s="4" t="n">
-        <v>99.51000000000001</v>
-      </c>
-      <c r="H389" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>375.48</v>
+      </c>
+      <c r="H389" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="390">
@@ -17190,7 +17326,7 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C390" s="3" t="inlineStr">
@@ -17200,12 +17336,12 @@
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>252549305-006</t>
+          <t>58542308</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>375/0525 FENCE MODULAR 12' L X 6' H TEMPORARY PAN</t>
+          <t>Felt Filter Bag for Water, Sewn Seam, 7" Diameter</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr">
@@ -17214,12 +17350,10 @@
         </is>
       </c>
       <c r="G390" s="4" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="H390" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>228.25</v>
+      </c>
+      <c r="H390" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="391">
@@ -17228,7 +17362,7 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C391" s="3" t="inlineStr">
@@ -17238,12 +17372,12 @@
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>252549305-006</t>
+          <t>58542308</t>
         </is>
       </c>
       <c r="E391" s="3" t="inlineStr">
         <is>
-          <t>Fence Wheel and weight</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F391" s="3" t="inlineStr">
@@ -17252,12 +17386,10 @@
         </is>
       </c>
       <c r="G391" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="H391" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>17.69</v>
+      </c>
+      <c r="H391" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="392">
@@ -17266,7 +17398,7 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C392" s="3" t="inlineStr">
@@ -17276,12 +17408,12 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>252549305-006</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Service Charge and Tax</t>
+          <t>2 LONG RADIUS 45 ELBOW WELD HEAT</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr">
@@ -17290,12 +17422,10 @@
         </is>
       </c>
       <c r="G392" s="4" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="H392" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>84.95999999999999</v>
+      </c>
+      <c r="H392" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="393">
@@ -17304,7 +17434,7 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C393" s="3" t="inlineStr">
@@ -17314,12 +17444,12 @@
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>58542308</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E393" s="3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>WLDCAP2</t>
         </is>
       </c>
       <c r="F393" s="3" t="inlineStr">
@@ -17328,12 +17458,10 @@
         </is>
       </c>
       <c r="G393" s="4" t="n">
-        <v>20.23</v>
-      </c>
-      <c r="H393" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>86.40000000000001</v>
+      </c>
+      <c r="H393" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="394">
@@ -17342,7 +17470,7 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C394" s="3" t="inlineStr">
@@ -17357,7 +17485,7 @@
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>2 LONG RADIUS 90 ELBOW WELD HEAT</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr">
@@ -17366,45 +17494,43 @@
         </is>
       </c>
       <c r="G394" s="4" t="n">
-        <v>124.87</v>
-      </c>
-      <c r="H394" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>265.65</v>
+      </c>
+      <c r="H394" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E395" s="3" t="inlineStr">
         <is>
-          <t>Luke Giguere per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
         </is>
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G395" s="4" t="n">
-        <v>350</v>
+        <v>202.6</v>
       </c>
       <c r="H395" s="5" t="n">
         <v>500</v>
@@ -17412,35 +17538,35 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+          <t>2 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G396" s="4" t="n">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="H396" s="5" t="n">
         <v>500</v>
@@ -17448,35 +17574,35 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E397" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt per diem Per diem for week of 1/17/2026 - 1/18/2026</t>
+          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
         </is>
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G397" s="4" t="n">
-        <v>100</v>
+        <v>290.4</v>
       </c>
       <c r="H397" s="5" t="n">
         <v>500</v>
@@ -17484,35 +17610,35 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Vace Varasteh per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+          <t>2 TEE WELD HEAT</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G398" s="4" t="n">
-        <v>350</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H398" s="5" t="n">
         <v>500</v>
@@ -17520,35 +17646,35 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>Vace Varasteh per diem Per diem for week of 1/9/2026 - 1/11/2026</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G399" s="4" t="n">
-        <v>150</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H399" s="5" t="n">
         <v>500</v>
@@ -17556,11 +17682,11 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C400" s="3" t="inlineStr">
@@ -17570,12 +17696,12 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>9784026081</t>
+          <t>252549305-006</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>GATE VALVE,1",BRASS,NPT</t>
+          <t>375/0525 FENCE MODULAR 12' L X 6' H TEMPORARY PAN</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr">
@@ -17584,21 +17710,19 @@
         </is>
       </c>
       <c r="G400" s="4" t="n">
-        <v>2022.75</v>
-      </c>
-      <c r="H400" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>58.1</v>
+      </c>
+      <c r="H400" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C401" s="3" t="inlineStr">
@@ -17608,12 +17732,12 @@
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>9784026081</t>
+          <t>252549305-006</t>
         </is>
       </c>
       <c r="E401" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Fence Wheel and weight</t>
         </is>
       </c>
       <c r="F401" s="3" t="inlineStr">
@@ -17622,21 +17746,19 @@
         </is>
       </c>
       <c r="G401" s="4" t="n">
-        <v>189.64</v>
-      </c>
-      <c r="H401" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>65</v>
+      </c>
+      <c r="H401" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>46051</v>
+        <v>46044</v>
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C402" s="3" t="inlineStr">
@@ -17646,12 +17768,12 @@
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>1611105730-1</t>
+          <t>252549305-006</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>2 CAP WELD HEAT</t>
+          <t>Service Charge and Tax</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr">
@@ -17660,21 +17782,19 @@
         </is>
       </c>
       <c r="G402" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H402" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>12.56</v>
+      </c>
+      <c r="H402" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>46051</v>
+        <v>46044</v>
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C403" s="3" t="inlineStr">
@@ -17684,12 +17804,12 @@
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>1611105730-1</t>
+          <t>58542308</t>
         </is>
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F403" s="3" t="inlineStr">
@@ -17698,21 +17818,19 @@
         </is>
       </c>
       <c r="G403" s="4" t="n">
-        <v>526.76</v>
-      </c>
-      <c r="H403" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>20.23</v>
+      </c>
+      <c r="H403" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>46051</v>
+        <v>46044</v>
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C404" s="3" t="inlineStr">
@@ -17722,12 +17840,12 @@
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>1611105730-1</t>
+          <t>1611105730</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr">
@@ -17736,55 +17854,51 @@
         </is>
       </c>
       <c r="G404" s="4" t="n">
-        <v>50.73</v>
-      </c>
-      <c r="H404" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>124.87</v>
+      </c>
+      <c r="H404" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="B405" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>IN222703</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="E405" s="3" t="inlineStr">
         <is>
-          <t>10' galv spiral pipe 1- ft 26 ga</t>
+          <t>Luke Giguere per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
         </is>
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="G405" s="4" t="n">
-        <v>1925</v>
-      </c>
-      <c r="H405" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>350</v>
+      </c>
+      <c r="H405" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
@@ -17798,12 +17912,12 @@
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Luke Giguere Per diem for week of 2/2/2026 - 2/8/2026</t>
+          <t>Michael Hyatt per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr">
@@ -17814,15 +17928,13 @@
       <c r="G406" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="H406" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H406" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
@@ -17836,12 +17948,12 @@
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt Per diem for week of 2/2/2026 - 2/8/2026</t>
+          <t>Michael Hyatt per diem Per diem for week of 1/17/2026 - 1/18/2026</t>
         </is>
       </c>
       <c r="F407" s="3" t="inlineStr">
@@ -17850,17 +17962,15 @@
         </is>
       </c>
       <c r="G407" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="H407" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H407" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>46055</v>
+        <v>46045</v>
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
@@ -17874,12 +17984,12 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>Vace Varasteh Per diem for week of 2/2/2026 - 2/8/2026</t>
+          <t>Vace Varasteh per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr">
@@ -17890,53 +18000,49 @@
       <c r="G408" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="H408" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H408" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>1611148835</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>2 BLK PE A53B SCH40 STEEL PIPE .154W HEAT</t>
+          <t>Vace Varasteh per diem Per diem for week of 1/9/2026 - 1/11/2026</t>
         </is>
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="G409" s="4" t="n">
-        <v>745.9</v>
-      </c>
-      <c r="H409" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>150</v>
+      </c>
+      <c r="H409" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
@@ -17950,12 +18056,12 @@
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>1611148835</t>
+          <t>9784026081</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>2 LONG RADIUS 45 ELBOW WELD HEAT</t>
+          <t>GATE VALVE,1",BRASS,NPT</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr">
@@ -17964,17 +18070,15 @@
         </is>
       </c>
       <c r="G410" s="4" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="H410" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>2022.75</v>
+      </c>
+      <c r="H410" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
@@ -17988,12 +18092,12 @@
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>1611148835</t>
+          <t>9784026081</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F411" s="3" t="inlineStr">
@@ -18002,55 +18106,47 @@
         </is>
       </c>
       <c r="G411" s="4" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="H411" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>189.64</v>
+      </c>
+      <c r="H411" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D412" s="3" t="inlineStr">
-        <is>
-          <t>1611148835</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D412" s="3" t="inlineStr"/>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>2 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+          <t>Vace Varasteh	Hotel- 1/26-2/5</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G412" s="4" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="H412" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>1053.12</v>
+      </c>
+      <c r="H412" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
@@ -18064,12 +18160,12 @@
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>1611148835</t>
+          <t>1611105730-1</t>
         </is>
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
+          <t>2 CAP WELD HEAT</t>
         </is>
       </c>
       <c r="F413" s="3" t="inlineStr">
@@ -18078,17 +18174,15 @@
         </is>
       </c>
       <c r="G413" s="4" t="n">
-        <v>13.84</v>
-      </c>
-      <c r="H413" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>14.4</v>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
@@ -18102,12 +18196,12 @@
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>1611148835</t>
+          <t>1611105730-1</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr">
@@ -18116,21 +18210,19 @@
         </is>
       </c>
       <c r="G414" s="4" t="n">
-        <v>73.88</v>
-      </c>
-      <c r="H414" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>526.76</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>46057</v>
+        <v>46051</v>
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>5112 · Carbon &amp; Lab Samplies (Driect)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C415" s="3" t="inlineStr">
@@ -18140,12 +18232,12 @@
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>CSI 134-26</t>
+          <t>1611105730-1</t>
         </is>
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>55 Gallon Liquid Phase Filter Drums filled with Liquid Phase Coconut Shell Activated Carbon</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="F415" s="3" t="inlineStr">
@@ -18154,131 +18246,115 @@
         </is>
       </c>
       <c r="G415" s="4" t="n">
-        <v>2600</v>
-      </c>
-      <c r="H415" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>50.73</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D416" s="3" t="inlineStr">
-        <is>
-          <t>CSI 134-26</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D416" s="3" t="inlineStr"/>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>EMILY G SANDOVAL-81047-189158      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G416" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="H416" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>1053.04</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5107 · Travel - Other (Direct)</t>
         </is>
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
-        </is>
-      </c>
-      <c r="D417" s="3" t="inlineStr">
-        <is>
-          <t>16818</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D417" s="3" t="inlineStr"/>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt Per diem for week of 2/9/2026 - 2/15/2026</t>
+          <t>Luke Gigure	Flight- SJC to BGR 2/2</t>
         </is>
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G417" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="H417" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>450.5</v>
+      </c>
+      <c r="H417" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>IN222703</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Mike Cogswell Per diem for week of 2/9/2026 - 2/15/2026</t>
+          <t>10' galv spiral pipe 1- ft 26 ga</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G418" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="H418" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>1925</v>
+      </c>
+      <c r="H418" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>46059</v>
+        <v>46055</v>
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
@@ -18292,12 +18368,12 @@
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>Vace Varasteh Per diem for week of 2/9/2026 - 2/15/2026</t>
+          <t>Michael Hyatt Per diem for week of 2/2/2026 - 2/8/2026</t>
         </is>
       </c>
       <c r="F419" s="3" t="inlineStr">
@@ -18308,129 +18384,113 @@
       <c r="G419" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="H419" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H419" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>46059</v>
+        <v>46055</v>
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>3 LONG RADIUS 90 ELBOW WELD HEAT</t>
+          <t>Vace Varasteh Per diem for week of 2/2/2026 - 2/8/2026</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="G420" s="4" t="n">
-        <v>258.15</v>
-      </c>
-      <c r="H420" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>350</v>
+      </c>
+      <c r="H420" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D421" s="3" t="inlineStr">
-        <is>
-          <t>1611156933</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D421" s="3" t="inlineStr"/>
       <c r="E421" s="3" t="inlineStr">
         <is>
-          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+          <t>Vace Varasteh	Hotel- 1/26-2/5</t>
         </is>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G421" s="4" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="H421" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>1001.42</v>
+      </c>
+      <c r="H421" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="D422" s="3" t="inlineStr">
-        <is>
-          <t>1611156933</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="inlineStr"/>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>3 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+          <t>EMILY G SANDOVAL-81047-189158      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G422" s="4" t="n">
-        <v>274.56</v>
-      </c>
-      <c r="H422" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>479.4</v>
+      </c>
+      <c r="H422" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
@@ -18444,12 +18504,12 @@
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>9168945440</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr">
         <is>
-          <t>6 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+          <t>Welding Rod</t>
         </is>
       </c>
       <c r="F423" s="3" t="inlineStr">
@@ -18458,17 +18518,15 @@
         </is>
       </c>
       <c r="G423" s="4" t="n">
-        <v>285.6</v>
-      </c>
-      <c r="H423" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>395.98</v>
+      </c>
+      <c r="H423" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
@@ -18482,12 +18540,12 @@
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>1611148835</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>3 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+          <t>2 BLK PE A53B SCH40 STEEL PIPE .154W HEAT</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr">
@@ -18496,17 +18554,15 @@
         </is>
       </c>
       <c r="G424" s="4" t="n">
-        <v>26.16</v>
-      </c>
-      <c r="H424" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>745.9</v>
+      </c>
+      <c r="H424" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
@@ -18520,12 +18576,12 @@
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>1611148835</t>
         </is>
       </c>
       <c r="E425" s="3" t="inlineStr">
         <is>
-          <t>6 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+          <t>2 LONG RADIUS 45 ELBOW WELD HEAT</t>
         </is>
       </c>
       <c r="F425" s="3" t="inlineStr">
@@ -18534,17 +18590,15 @@
         </is>
       </c>
       <c r="G425" s="4" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="H425" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>10.78</v>
+      </c>
+      <c r="H425" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
@@ -18558,12 +18612,12 @@
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>1611148835</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>6 BOLT SET PLTD 307A (8) 3/4 X 3 1/4</t>
+          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr">
@@ -18572,17 +18626,15 @@
         </is>
       </c>
       <c r="G426" s="4" t="n">
-        <v>173.96</v>
-      </c>
-      <c r="H426" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>14.66</v>
+      </c>
+      <c r="H426" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
@@ -18596,12 +18648,12 @@
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>1611148835</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
+          <t>2 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
         </is>
       </c>
       <c r="F427" s="3" t="inlineStr">
@@ -18610,17 +18662,15 @@
         </is>
       </c>
       <c r="G427" s="4" t="n">
-        <v>83.04000000000001</v>
-      </c>
-      <c r="H427" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>2.83</v>
+      </c>
+      <c r="H427" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
@@ -18634,12 +18684,12 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>1611148835</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>6 X 3 CONC REDUCER WELD HEAT</t>
+          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr">
@@ -18648,17 +18698,15 @@
         </is>
       </c>
       <c r="G428" s="4" t="n">
-        <v>29.73</v>
-      </c>
-      <c r="H428" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>13.84</v>
+      </c>
+      <c r="H428" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
@@ -18672,7 +18720,7 @@
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>1611156933</t>
+          <t>1611148835</t>
         </is>
       </c>
       <c r="E429" s="3" t="inlineStr">
@@ -18686,164 +18734,2450 @@
         </is>
       </c>
       <c r="G429" s="4" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="H429" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>73.88</v>
+      </c>
+      <c r="H429" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>46065</v>
+        <v>46057</v>
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5112 · Carbon &amp; Lab Samplies (Driect)</t>
         </is>
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>CSI 134-26</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Vace Varasteh Per diem for week of 2/16/2026 - 2/22/2026</t>
+          <t>55 Gallon Liquid Phase Filter Drums filled with Liquid Phase Coconut Shell Activated Carbon</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G430" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="H430" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>2600</v>
+      </c>
+      <c r="H430" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>46065</v>
+        <v>46057</v>
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>CSI 134-26</t>
         </is>
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt Per diem for week of 2/16/2026 - 2/22/2026</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="G431" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="H431" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H431" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>46073</v>
+        <v>46058</v>
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
-        </is>
-      </c>
-      <c r="D432" s="3" t="inlineStr">
-        <is>
-          <t>16822</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D432" s="3" t="inlineStr"/>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>Michael Hyatt Per diem for week of 2/23/2026 - 3/1/2026</t>
+          <t>EMILY G SANDOVAL-81047-189157      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="G432" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="H432" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>1053.12</v>
+      </c>
+      <c r="H432" s="5" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>5107 · Travel - Other (Direct)</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D433" s="3" t="inlineStr">
+        <is>
+          <t>ER 011926</t>
+        </is>
+      </c>
+      <c r="E433" s="3" t="inlineStr">
+        <is>
+          <t>taxi for ride to airport</t>
+        </is>
+      </c>
+      <c r="F433" s="3" t="inlineStr">
+        <is>
+          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
+        </is>
+      </c>
+      <c r="G433" s="4" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="H433" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>5107 · Travel - Other (Direct)</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D434" s="3" t="inlineStr">
+        <is>
+          <t>ER 012026</t>
+        </is>
+      </c>
+      <c r="E434" s="3" t="inlineStr">
+        <is>
+          <t>uber for ride to airport</t>
+        </is>
+      </c>
+      <c r="F434" s="3" t="inlineStr">
+        <is>
+          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
+        </is>
+      </c>
+      <c r="G434" s="4" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="H434" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D435" s="3" t="inlineStr">
+        <is>
+          <t>66477</t>
+        </is>
+      </c>
+      <c r="E435" s="3" t="inlineStr">
+        <is>
+          <t>Hex Cap Screws</t>
+        </is>
+      </c>
+      <c r="F435" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G435" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H435" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>66477</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="inlineStr">
+        <is>
+          <t>Flat Washers</t>
+        </is>
+      </c>
+      <c r="F436" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G436" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H436" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B437" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C437" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D437" s="3" t="inlineStr">
+        <is>
+          <t>66477</t>
+        </is>
+      </c>
+      <c r="E437" s="3" t="inlineStr">
+        <is>
+          <t>Phil Pan MS</t>
+        </is>
+      </c>
+      <c r="F437" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G437" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H437" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>66477</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="inlineStr">
+        <is>
+          <t>Flat Washers</t>
+        </is>
+      </c>
+      <c r="F438" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G438" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H438" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C439" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D439" s="3" t="inlineStr">
+        <is>
+          <t>66477</t>
+        </is>
+      </c>
+      <c r="E439" s="3" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="F439" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G439" s="4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H439" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D440" s="3" t="inlineStr">
+        <is>
+          <t>66484</t>
+        </is>
+      </c>
+      <c r="E440" s="3" t="inlineStr">
+        <is>
+          <t>Worm Clamp</t>
+        </is>
+      </c>
+      <c r="F440" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G440" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="H440" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>66484</t>
+        </is>
+      </c>
+      <c r="E441" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F441" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G441" s="4" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="H441" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>5106 · Travel - Hotel (Direct)</t>
+        </is>
+      </c>
+      <c r="C442" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D442" s="3" t="inlineStr"/>
+      <c r="E442" s="3" t="inlineStr">
+        <is>
+          <t>EMILY G SANDOVAL-81047-189157      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
+        </is>
+      </c>
+      <c r="F442" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G442" s="4" t="n">
+        <v>161.64</v>
+      </c>
+      <c r="H442" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C443" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="D443" s="3" t="inlineStr">
+        <is>
+          <t>16818</t>
+        </is>
+      </c>
+      <c r="E443" s="3" t="inlineStr">
+        <is>
+          <t>Michael Hyatt Per diem for week of 2/9/2026 - 2/15/2026</t>
+        </is>
+      </c>
+      <c r="F443" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="G443" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="H443" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>16818</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="inlineStr">
+        <is>
+          <t>Vace Varasteh Per diem for week of 2/9/2026 - 2/15/2026</t>
+        </is>
+      </c>
+      <c r="F444" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="G444" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="H444" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C445" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D445" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E445" s="3" t="inlineStr">
+        <is>
+          <t>3 LONG RADIUS 90 ELBOW WELD HEAT</t>
+        </is>
+      </c>
+      <c r="F445" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G445" s="4" t="n">
+        <v>258.15</v>
+      </c>
+      <c r="H445" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C446" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D446" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E446" s="3" t="inlineStr">
+        <is>
+          <t>2 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+        </is>
+      </c>
+      <c r="F446" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G446" s="4" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="H446" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C447" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D447" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E447" s="3" t="inlineStr">
+        <is>
+          <t>3 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+        </is>
+      </c>
+      <c r="F447" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G447" s="4" t="n">
+        <v>274.56</v>
+      </c>
+      <c r="H447" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C448" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D448" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E448" s="3" t="inlineStr">
+        <is>
+          <t>6 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+        </is>
+      </c>
+      <c r="F448" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G448" s="4" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="H448" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C449" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D449" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E449" s="3" t="inlineStr">
+        <is>
+          <t>3 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+        </is>
+      </c>
+      <c r="F449" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G449" s="4" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="H449" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C450" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D450" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E450" s="3" t="inlineStr">
+        <is>
+          <t>6 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+        </is>
+      </c>
+      <c r="F450" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G450" s="4" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="H450" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B451" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C451" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D451" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E451" s="3" t="inlineStr">
+        <is>
+          <t>6 BOLT SET PLTD 307A (8) 3/4 X 3 1/4</t>
+        </is>
+      </c>
+      <c r="F451" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G451" s="4" t="n">
+        <v>173.96</v>
+      </c>
+      <c r="H451" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C452" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D452" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E452" s="3" t="inlineStr">
+        <is>
+          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
+        </is>
+      </c>
+      <c r="F452" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G452" s="4" t="n">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="H452" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B453" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C453" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D453" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E453" s="3" t="inlineStr">
+        <is>
+          <t>6 X 3 CONC REDUCER WELD HEAT</t>
+        </is>
+      </c>
+      <c r="F453" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G453" s="4" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="H453" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C454" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D454" s="3" t="inlineStr">
+        <is>
+          <t>1611156933</t>
+        </is>
+      </c>
+      <c r="E454" s="3" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="F454" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G454" s="4" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="H454" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B455" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C455" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D455" s="3" t="inlineStr">
+        <is>
+          <t>9169114912</t>
+        </is>
+      </c>
+      <c r="E455" s="3" t="inlineStr">
+        <is>
+          <t>Welding Rod</t>
+        </is>
+      </c>
+      <c r="F455" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G455" s="4" t="n">
+        <v>128.02</v>
+      </c>
+      <c r="H455" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>5106 · Travel - Hotel (Direct)</t>
+        </is>
+      </c>
+      <c r="C456" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D456" s="3" t="inlineStr"/>
+      <c r="E456" s="3" t="inlineStr">
+        <is>
+          <t>EMILY G SANDOVAL-81047-191173      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
+        </is>
+      </c>
+      <c r="F456" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G456" s="4" t="n">
+        <v>1331.18</v>
+      </c>
+      <c r="H456" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B457" s="3" t="inlineStr">
+        <is>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
+        </is>
+      </c>
+      <c r="C457" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D457" s="3" t="inlineStr">
+        <is>
+          <t>3106994</t>
+        </is>
+      </c>
+      <c r="E457" s="3" t="inlineStr">
+        <is>
+          <t>Orange to San Jose</t>
+        </is>
+      </c>
+      <c r="F457" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G457" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H457" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>5106 · Travel - Hotel (Direct)</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D458" s="3" t="inlineStr"/>
+      <c r="E458" s="3" t="inlineStr">
+        <is>
+          <t>EMILY G SANDOVAL-81047-189157      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
+        </is>
+      </c>
+      <c r="F458" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G458" s="4" t="n">
+        <v>1063.64</v>
+      </c>
+      <c r="H458" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B459" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C459" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D459" s="3" t="inlineStr">
+        <is>
+          <t>1611156933-1</t>
+        </is>
+      </c>
+      <c r="E459" s="3" t="inlineStr">
+        <is>
+          <t>6 X 3 CONC REDUCER WELD HEAT #______________________________</t>
+        </is>
+      </c>
+      <c r="F459" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G459" s="4" t="n">
+        <v>178.38</v>
+      </c>
+      <c r="H459" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C460" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>1611156933-1</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="inlineStr">
+        <is>
+          <t>3 TEE WELD HEAT</t>
+        </is>
+      </c>
+      <c r="F460" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G460" s="4" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="H460" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B461" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C461" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D461" s="3" t="inlineStr">
+        <is>
+          <t>1611156933-1</t>
+        </is>
+      </c>
+      <c r="E461" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F461" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G461" s="4" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="H461" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D462" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0001</t>
+        </is>
+      </c>
+      <c r="E462" s="3" t="inlineStr">
+        <is>
+          <t>1.00 1000LB DSL TRACK MINI SKIDSTEER</t>
+        </is>
+      </c>
+      <c r="F462" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G462" s="4" t="n">
+        <v>2965</v>
+      </c>
+      <c r="H462" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B463" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C463" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D463" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0001</t>
+        </is>
+      </c>
+      <c r="E463" s="3" t="inlineStr">
+        <is>
+          <t>10K 42'-48' TELEHANDLER FORKLIFT</t>
+        </is>
+      </c>
+      <c r="F463" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G463" s="4" t="n">
+        <v>4870</v>
+      </c>
+      <c r="H463" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C464" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D464" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0001</t>
+        </is>
+      </c>
+      <c r="E464" s="3" t="inlineStr">
+        <is>
+          <t>Service fees</t>
+        </is>
+      </c>
+      <c r="F464" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G464" s="4" t="n">
+        <v>304.14</v>
+      </c>
+      <c r="H464" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C465" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D465" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0001</t>
+        </is>
+      </c>
+      <c r="E465" s="3" t="inlineStr">
+        <is>
+          <t>Delivery &amp; Pick Up</t>
+        </is>
+      </c>
+      <c r="F465" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G465" s="4" t="n">
+        <v>520</v>
+      </c>
+      <c r="H465" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C466" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D466" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0001</t>
+        </is>
+      </c>
+      <c r="E466" s="3" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="F466" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G466" s="4" t="n">
+        <v>791.36</v>
+      </c>
+      <c r="H466" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B467" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C467" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="D467" s="3" t="inlineStr">
+        <is>
+          <t>16821</t>
+        </is>
+      </c>
+      <c r="E467" s="3" t="inlineStr">
+        <is>
+          <t>Vace Varasteh Per diem for week of 2/16/2026 - 2/22/2026</t>
+        </is>
+      </c>
+      <c r="F467" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="G467" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="H467" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C468" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="D468" s="3" t="inlineStr">
+        <is>
+          <t>16821</t>
+        </is>
+      </c>
+      <c r="E468" s="3" t="inlineStr">
+        <is>
+          <t>Michael Hyatt Per diem for week of 2/16/2026 - 2/22/2026</t>
+        </is>
+      </c>
+      <c r="F468" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="G468" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="H468" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C469" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D469" s="3" t="inlineStr">
+        <is>
+          <t>252549305-007</t>
+        </is>
+      </c>
+      <c r="E469" s="3" t="inlineStr">
+        <is>
+          <t>375/0525 FENCE MODULAR 12' L X 6' H TEMPORARY PAN</t>
+        </is>
+      </c>
+      <c r="F469" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G469" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="H469" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D470" s="3" t="inlineStr">
+        <is>
+          <t>252549305-007</t>
+        </is>
+      </c>
+      <c r="E470" s="3" t="inlineStr">
+        <is>
+          <t>Fence Wheel and weight</t>
+        </is>
+      </c>
+      <c r="F470" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G470" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="H470" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C471" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D471" s="3" t="inlineStr">
+        <is>
+          <t>252549305-007</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="inlineStr">
+        <is>
+          <t>Service Charge and Tax</t>
+        </is>
+      </c>
+      <c r="F471" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G471" s="4" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="H471" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B433" s="3" t="inlineStr">
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>5106 · Travel - Hotel (Direct)</t>
+        </is>
+      </c>
+      <c r="C472" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D472" s="3" t="inlineStr"/>
+      <c r="E472" s="3" t="inlineStr">
+        <is>
+          <t>EMILY G SANDOVAL-81047-189157      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
+        </is>
+      </c>
+      <c r="F472" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G472" s="4" t="n">
+        <v>1019.76</v>
+      </c>
+      <c r="H472" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B473" s="3" t="inlineStr">
+        <is>
+          <t>5106 · Travel - Hotel (Direct)</t>
+        </is>
+      </c>
+      <c r="C473" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D473" s="3" t="inlineStr"/>
+      <c r="E473" s="3" t="inlineStr">
+        <is>
+          <t>EMILY G SANDOVAL-81047-191173      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
+        </is>
+      </c>
+      <c r="F473" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G473" s="4" t="n">
+        <v>1070.6</v>
+      </c>
+      <c r="H473" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
         <is>
           <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
-      <c r="C433" s="3" t="inlineStr">
+      <c r="C474" s="3" t="inlineStr">
         <is>
           <t>General Journal</t>
         </is>
       </c>
-      <c r="D433" s="3" t="inlineStr">
+      <c r="D474" s="3" t="inlineStr">
         <is>
           <t>16822</t>
         </is>
       </c>
-      <c r="E433" s="3" t="inlineStr">
+      <c r="E474" s="3" t="inlineStr">
+        <is>
+          <t>Michael Hyatt Per diem for week of 2/23/2026 - 3/1/2026</t>
+        </is>
+      </c>
+      <c r="F474" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="G474" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="H474" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B475" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C475" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="D475" s="3" t="inlineStr">
+        <is>
+          <t>16822</t>
+        </is>
+      </c>
+      <c r="E475" s="3" t="inlineStr">
         <is>
           <t>Vace Varasteh Per diem for week of 2/23/2026 - 3/1/2026</t>
         </is>
       </c>
-      <c r="F433" s="3" t="inlineStr">
+      <c r="F475" s="3" t="inlineStr">
         <is>
           <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
-      <c r="G433" s="4" t="n">
+      <c r="G475" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="H433" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="H475" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C476" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D476" s="3" t="inlineStr">
+        <is>
+          <t>1611191957</t>
+        </is>
+      </c>
+      <c r="E476" s="3" t="inlineStr">
+        <is>
+          <t>BLK T&amp;C A53A SCH40 STEEL PIPE</t>
+        </is>
+      </c>
+      <c r="F476" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G476" s="4" t="n">
+        <v>478.09</v>
+      </c>
+      <c r="H476" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B477" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C477" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D477" s="3" t="inlineStr">
+        <is>
+          <t>1611191957</t>
+        </is>
+      </c>
+      <c r="E477" s="3" t="inlineStr">
+        <is>
+          <t>3 150# RF SLIP-ON WELD FLANGE A105 HEAT</t>
+        </is>
+      </c>
+      <c r="F477" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G477" s="4" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="H477" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D478" s="3" t="inlineStr">
+        <is>
+          <t>1611191957</t>
+        </is>
+      </c>
+      <c r="E478" s="3" t="inlineStr">
+        <is>
+          <t>3 150# 1/16 FULL FACE GASKET NON-ASBESTOS FIBER</t>
+        </is>
+      </c>
+      <c r="F478" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G478" s="4" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H478" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C479" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D479" s="3" t="inlineStr">
+        <is>
+          <t>1611191957</t>
+        </is>
+      </c>
+      <c r="E479" s="3" t="inlineStr">
+        <is>
+          <t>2 - 3 BOLT SET PLTD 307A (4) 5/8 X 3</t>
+        </is>
+      </c>
+      <c r="F479" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G479" s="4" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="H479" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>1611191957</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="inlineStr">
+        <is>
+          <t>1 QT DARK CUTTING OIL HERCULES</t>
+        </is>
+      </c>
+      <c r="F480" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G480" s="4" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="H480" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D481" s="3" t="inlineStr">
+        <is>
+          <t>1611191957</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="inlineStr">
+        <is>
+          <t>1 5/8*1 5/8*20' HALF SLOT 12GA CHANNEL GALV</t>
+        </is>
+      </c>
+      <c r="F481" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G481" s="4" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="H481" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D482" s="3" t="inlineStr">
+        <is>
+          <t>1611191957</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="inlineStr">
+        <is>
+          <t>TAx</t>
+        </is>
+      </c>
+      <c r="F482" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G482" s="4" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="H482" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D483" s="3" t="inlineStr">
+        <is>
+          <t>180365208-0001</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>1/2" - 2" RIDGID 700 THREADER HANDHE</t>
+        </is>
+      </c>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G483" s="4" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="H483" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D484" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0002</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>1.00 1000LB DSL TRACK MINI SKIDSTEER</t>
+        </is>
+      </c>
+      <c r="F484" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G484" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H484" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B485" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C485" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D485" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0002</t>
+        </is>
+      </c>
+      <c r="E485" s="3" t="inlineStr">
+        <is>
+          <t>10K 42'-48' TELEHANDLER FORKLIFT</t>
+        </is>
+      </c>
+      <c r="F485" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G485" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D486" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0002</t>
+        </is>
+      </c>
+      <c r="E486" s="3" t="inlineStr">
+        <is>
+          <t>Service fees</t>
+        </is>
+      </c>
+      <c r="F486" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G486" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H486" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C487" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D487" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0002</t>
+        </is>
+      </c>
+      <c r="E487" s="3" t="inlineStr">
+        <is>
+          <t>Diesel Fuel</t>
+        </is>
+      </c>
+      <c r="F487" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G487" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="H487" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D488" s="3" t="inlineStr">
+        <is>
+          <t>179372899-0002</t>
+        </is>
+      </c>
+      <c r="E488" s="3" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="F488" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G488" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H488" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C489" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D489" s="3" t="inlineStr">
+        <is>
+          <t>321-T0000247</t>
+        </is>
+      </c>
+      <c r="E489" s="3" t="inlineStr">
+        <is>
+          <t>1 IN Suction Hose</t>
+        </is>
+      </c>
+      <c r="F489" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G489" s="4" t="n">
+        <v>1096.4</v>
+      </c>
+      <c r="H489" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>321-T0000247</t>
+        </is>
+      </c>
+      <c r="E490" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F490" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G490" s="4" t="n">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="H490" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B491" s="3" t="inlineStr">
+        <is>
+          <t>5105 · Travel - Airfare (Direct)</t>
+        </is>
+      </c>
+      <c r="C491" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D491" s="3" t="inlineStr"/>
+      <c r="E491" s="3" t="inlineStr">
+        <is>
+          <t>Carol Winell &amp; Iain C	Flight- LGB to SJC 3/3- SJC to LGB 3/3</t>
+        </is>
+      </c>
+      <c r="F491" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G491" s="4" t="n">
+        <v>263.8</v>
+      </c>
+      <c r="H491" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>5106 · Travel - Hotel (Direct)</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D492" s="3" t="inlineStr"/>
+      <c r="E492" s="3" t="inlineStr">
+        <is>
+          <t>EMILY G SANDOVAL-81047-189157      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
+        </is>
+      </c>
+      <c r="F492" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G492" s="4" t="n">
+        <v>832</v>
+      </c>
+      <c r="H492" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>5106 · Travel - Hotel (Direct)</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D493" s="3" t="inlineStr"/>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>EMILY G SANDOVAL-81047-191173      916-355-1616 LARKSPUR LANDING MILPITAS LARKSPUR LAN MILPITAS CA</t>
+        </is>
+      </c>
+      <c r="F493" s="3" t="inlineStr">
+        <is>
+          <t>2310 · American Express Delta</t>
+        </is>
+      </c>
+      <c r="G493" s="4" t="n">
+        <v>904.48</v>
+      </c>
+      <c r="H493" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>5107.1 · Travel - Car Rental</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="D494" s="3" t="inlineStr"/>
+      <c r="E494" s="3" t="inlineStr"/>
+      <c r="F494" s="3" t="inlineStr">
+        <is>
+          <t>2321 · Commerce Bank - Enterprise Acct</t>
+        </is>
+      </c>
+      <c r="G494" s="4" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="H494" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D495" s="3" t="inlineStr">
+        <is>
+          <t>321-T0000427</t>
+        </is>
+      </c>
+      <c r="E495" s="3" t="inlineStr">
+        <is>
+          <t>1 IN SUCTION HOSE</t>
+        </is>
+      </c>
+      <c r="F495" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G495" s="4" t="n">
+        <v>877.12</v>
+      </c>
+      <c r="H495" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D496" s="3" t="inlineStr">
+        <is>
+          <t>321-T0000427</t>
+        </is>
+      </c>
+      <c r="E496" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F496" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G496" s="4" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="H496" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D497" s="3" t="inlineStr">
+        <is>
+          <t>67050</t>
+        </is>
+      </c>
+      <c r="E497" s="3" t="inlineStr">
+        <is>
+          <t>1''- 2'' WORM CLAMP ALL STAINLESS STEEL</t>
+        </is>
+      </c>
+      <c r="F497" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G497" s="4" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="H497" s="5" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>5112 · Carbon &amp; Lab Samplies (Driect)</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D498" s="3" t="inlineStr">
+        <is>
+          <t>CSI 287-26</t>
+        </is>
+      </c>
+      <c r="E498" s="3" t="inlineStr">
+        <is>
+          <t>4x8 mesh Vapor Reactivated Carbon Media</t>
+        </is>
+      </c>
+      <c r="F498" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="G498" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H498" s="5" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
